--- a/data/templates/products_template.xlsx
+++ b/data/templates/products_template.xlsx
@@ -429,42 +429,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>variety</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>stem_length</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>stem_length</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>base_cost</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>base_cost</t>
+          <t>current_stock</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>current_stock</t>
+          <t>sale_enabled</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>sale_enabled</t>
+          <t>last_price</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>last_price</t>
+          <t>recommended_price</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
